--- a/downloads/korea-1924-25-tables.xlsx
+++ b/downloads/korea-1924-25-tables.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Annual Report on Reforms and Progress in Chosen 1924-25 — tables</t>
+          <t>Annual Report on Administration of Chosen 1924-26 — tables</t>
         </is>
       </c>
     </row>
